--- a/JsonConverter/ExcelFiles/Fixer.xlsx
+++ b/JsonConverter/ExcelFiles/Fixer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SunnyHoGaming\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_3632E3763A4F0F1F73740BCF85E6D9D6EE4EC956" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B474268-186A-4582-815D-0F7B632ECCE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="420" yWindow="1665" windowWidth="28185" windowHeight="12795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="90" yWindow="1065" windowWidth="28185" windowHeight="12795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Fixer" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
   <si>
     <t>암스트숏</t>
   </si>
@@ -64,62 +64,65 @@
     <t>ElectRepair</t>
   </si>
   <si>
+    <t>O2Repair</t>
+  </si>
+  <si>
+    <t>WayRepair</t>
+  </si>
+  <si>
+    <t>PrefabPath</t>
+  </si>
+  <si>
+    <t>SoundPath</t>
+  </si>
+  <si>
+    <t>TempRepair</t>
+  </si>
+  <si>
+    <t>해금 날짜</t>
+  </si>
+  <si>
+    <t>소리 경로</t>
+  </si>
+  <si>
+    <t>Speed</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>프리팹 경로</t>
+  </si>
+  <si>
+    <t>이동 속도</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>(name)</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>Fixer_01</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fixer_02</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>Fixer_03</t>
-  </si>
-  <si>
-    <t>O2Repair</t>
-  </si>
-  <si>
-    <t>WayRepair</t>
-  </si>
-  <si>
-    <t>PrefabPath</t>
-  </si>
-  <si>
-    <t>SoundPath</t>
-  </si>
-  <si>
-    <t>Fixer_02</t>
-  </si>
-  <si>
-    <t>TempRepair</t>
-  </si>
-  <si>
-    <t>Fixer_01</t>
-  </si>
-  <si>
-    <t>해금 날짜</t>
-  </si>
-  <si>
-    <t>소리 경로</t>
-  </si>
-  <si>
-    <t>Speed</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>프리팹 경로</t>
-  </si>
-  <si>
-    <t>이동 속도</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>(name)</t>
-  </si>
-  <si>
-    <t>string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -151,6 +154,12 @@
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -300,7 +309,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -336,6 +345,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -570,10 +580,10 @@
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>5</v>
@@ -591,45 +601,45 @@
         <v>4</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="12.75">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="11" customFormat="1" ht="15.75" customHeight="1">
@@ -637,39 +647,39 @@
         <v>7</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F3" s="14" t="s">
         <v>13</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H3" s="14" t="s">
         <v>2</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J3" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="11" t="s">
         <v>17</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>10</v>
@@ -678,7 +688,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
@@ -695,11 +705,13 @@
       <c r="I4" s="3">
         <v>100</v>
       </c>
-      <c r="J4" s="13"/>
+      <c r="J4" s="13" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>0</v>
@@ -708,7 +720,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="3">
         <v>100</v>
@@ -725,10 +737,13 @@
       <c r="I5" s="3">
         <v>100</v>
       </c>
+      <c r="J5" s="21" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>9</v>
@@ -737,7 +752,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="15">
         <v>100</v>
@@ -753,6 +768,9 @@
       </c>
       <c r="I6" s="3">
         <v>100</v>
+      </c>
+      <c r="J6" s="21" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1">
